--- a/bin/Debug/net8.0/Files/Prabhat Panel Chart.xlsx
+++ b/bin/Debug/net8.0/Files/Prabhat Panel Chart.xlsx
@@ -34463,13 +34463,13 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="E465" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F465" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G465" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="H465" s="3" t="s">
         <x:v>41</x:v>
